--- a/Несоответствие.xlsx
+++ b/Несоответствие.xlsx
@@ -492,7 +492,7 @@
     <row r="1" ht="48" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Несоответствие процесса обучения правилам обучения по охране труда, постановление Правительства РФ от 24.12.2021 № 2464</t>
+          <t>Несоответствия процесса обучения Правилам обучения по охране труда, утв. Постановлением Правительства РФ от 24.12.2021 № 2464</t>
         </is>
       </c>
     </row>

--- a/Несоответствие.xlsx
+++ b/Несоответствие.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Содержание пункта, с которым наблюдение расходится</t>
+          <t>Требование ПП 2464</t>
         </is>
       </c>
     </row>

--- a/Несоответствие.xlsx
+++ b/Несоответствие.xlsx
@@ -10,9 +10,9 @@
     <sheet name="Несоответствие" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Несоответствие'!$A$2:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Несоответствие'!$A$2:$E$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Несоответствие'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Несоответствие'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Несоответствие'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
@@ -534,23 +534,23 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Протокол ЮГОК без номера от 19 марта 2026 года для Гыргенова, программа 46б, длительность 330 часов.</t>
+          <t>Нет номера записи в реестре. Протокол ЮГОК ПГУ 26-40, по программе 46б указано 77 часов.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>п. 118, п. 46</t>
+          <t>п. 92</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>В реестр обученных лиц передают номер протокола проверки знания. Протокол без номера это требование не выполняет. Продолжительность программы 46б — не менее 16 часов; верхнего предела нет, поэтому 330 часов сами по себе норме не противоречат.</t>
+          <t>Регистрационный номер записи о прохождении проверки знания в реестре обученных лиц указывают в протоколе либо прикладывают подписанную электронной подписью выписку из реестра. 77 часов больше минимума в 16 часов и сами по себе не нарушение.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -559,23 +559,23 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Нет номера записи в реестре. Протокол ЮГОК ПГУ 26-40, по программе 46б указано 77 часов.</t>
+          <t>К протоколу ЮГОК ПГУ 26-40 приложен лист стажировки: стажировку начали раньше, чем проверку знания.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>п. 92</t>
+          <t>п. 25, п. 67</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Регистрационный номер записи о прохождении проверки знания в реестре обученных лиц указывают в протоколе либо прикладывают подписанную электронной подписью выписку из реестра. 77 часов больше минимума в 16 часов и сами по себе не нарушение.</t>
+          <t>К стажировке допускают работников, которые уже успешно прошли инструктаж по охране труда и обучение требованиям охраны труда по программам пункта 46. Обучение требованиям охраны труда заканчивается проверкой знания.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -584,23 +584,23 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>К протоколу ЮГОК ПГУ 26-40 приложен лист стажировки: стажировку начали раньше, чем проверку знания.</t>
+          <t>Программы стажировки все без подписи.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>п. 25, п. 67</t>
+          <t>п. 28</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>К стажировке допускают работников, которые уже успешно прошли инструктаж по охране труда и обучение требованиям охраны труда по программам пункта 46. Обучение требованиям охраны труда заканчивается проверкой знания.</t>
+          <t>Программу стажировки на рабочем месте или иной локальный акт, которым задан ее объем, утверждает работодатель.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -609,23 +609,23 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Программы стажировки все без подписи.</t>
+          <t>Программа 46а с 2023 года не утверждена.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>п. 28</t>
+          <t>п. 48</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Программу стажировки на рабочем месте или иной локальный акт, которым задан ее объем, утверждает работодатель.</t>
+          <t>Программу обучения требованиям охраны труда утверждает руководитель обучающей организации либо работодатель, если обучение проводит он.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -634,23 +634,23 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Программа 46а с 2023 года не утверждена.</t>
+          <t>В папке нет программы 46б.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>п. 48</t>
+          <t>п. 48, п. 96</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Программу обучения требованиям охраны труда утверждает руководитель обучающей организации либо работодатель, если обучение проводит он.</t>
+          <t>Программа обучения требованиям охраны труда должна быть разработана и утверждена. Работодатель, который обучает своих работников, обязан иметь программы и учебные материалы для каждой программы.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -659,23 +659,23 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>В папке нет программы 46б.</t>
+          <t>В журнале первичного инструктажа на рабочем месте даты идут не в хронологическом порядке, есть склеенные листы.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>п. 48, п. 96</t>
+          <t>п. 87, п. 88</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Программа обучения требованиям охраны труда должна быть разработана и утверждена. Работодатель, который обучает своих работников, обязан иметь программы и учебные материалы для каждой программы.</t>
+          <t>При регистрации инструктажа на рабочем месте указывают дату его проведения и остальные обязательные сведения. Порядок регистрации и форму утверждает работодатель. Запись должна позволять установить фактическую дату.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="72" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
@@ -684,23 +684,23 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>В журнале первичного инструктажа на рабочем месте даты идут не в хронологическом порядке, есть склеенные листы.</t>
+          <t>Внеплановый инструктаж по изменениям не проводили с сентября.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>п. 87, п. 88</t>
+          <t>п. 16, п. 17</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>При регистрации инструктажа на рабочем месте указывают дату его проведения и остальные обязательные сведения. Порядок регистрации и форму утверждает работодатель. Запись должна позволять установить фактическую дату.</t>
+          <t>Внеплановый инструктаж проводят, в частности, при изменении нормативных и локальных актов, которые затрагивают требования охраны труда и трудовые функции работника. Объем и сроки задает локальный акт работодателя.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="72" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
@@ -709,23 +709,23 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Внеплановый инструктаж по изменениям не проводили с сентября.</t>
+          <t>Проверку знания не проводят.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>п. 16, п. 17</t>
+          <t>п. 23, п. 67, п. 70</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Внеплановый инструктаж проводят, в частности, при изменении нормативных и локальных актов, которые затрагивают требования охраны труда и трудовые функции работника. Объем и сроки задает локальный акт работодателя.</t>
+          <t>Инструктаж по охране труда заканчивается проверкой знания требований охраны труда. Обучение по охране труда тоже завершается проверкой знания.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="72" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
@@ -734,23 +734,23 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Проверку знания не проводят.</t>
+          <t>В офисе на участке протокол проверки знания без подписей.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>п. 23, п. 67, п. 70</t>
+          <t>п. 93, п. 92</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Инструктаж по охране труда заканчивается проверкой знания требований охраны труда. Обучение по охране труда тоже завершается проверкой знания.</t>
+          <t>Протокол подписывают председатель и члены комиссии. В протоколе также должна быть подпись работника, прошедшего проверку знания.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
@@ -759,47 +759,23 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>В офисе на участке протокол проверки знания без подписей.</t>
+          <t>Протокол ЮГОК ЭУ 26-26: программу 46б прошли по инструкции по охране труда.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>п. 93, п. 92</t>
+          <t>п. 46, п. 48, п. 18</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Протокол подписывают председатель и члены комиссии. В протоколе также должна быть подпись работника, прошедшего проверку знания.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Несоответствие</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Протокол ЮГОК ЭУ 26-26: программу 46б прошли по инструкции по охране труда.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>п. 46, п. 48, п. 18</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
           <t>Программа 46б — обучение безопасным методам при вредных и опасных факторах продолжительностью не менее 16 часов. Ее разрабатывают по примерному перечню тем и утверждают. Инструкция по охране труда задает объем инструктажа на рабочем месте и программу 46б не заменяет.</t>
         </is>
       </c>
     </row>
+    <row r="13" ht="72" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A2:E13"/>
+  <autoFilter ref="A2:E12"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>

--- a/Несоответствие.xlsx
+++ b/Несоответствие.xlsx
@@ -10,9 +10,9 @@
     <sheet name="Несоответствие" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Несоответствие'!$A$2:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Несоответствие'!$A$2:$E$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Несоответствие'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Несоответствие'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Несоответствие'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
@@ -534,23 +534,23 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Нет номера записи в реестре. Протокол ЮГОК ПГУ 26-40, по программе 46б указано 77 часов.</t>
+          <t>Протокол ЮГОК без номера от 19 марта 2026 года для Гыргенова, программа 46б, длительность 330 часов.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>п. 92</t>
+          <t>п. 118, п. 46</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Регистрационный номер записи о прохождении проверки знания в реестре обученных лиц указывают в протоколе либо прикладывают подписанную электронной подписью выписку из реестра. 77 часов больше минимума в 16 часов и сами по себе не нарушение.</t>
+          <t>В реестр обученных лиц передают номер протокола проверки знания. Протокол без номера это требование не выполняет. Продолжительность программы 46б — не менее 16 часов; верхнего предела нет, поэтому 330 часов сами по себе норме не противоречат.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -559,23 +559,23 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>К протоколу ЮГОК ПГУ 26-40 приложен лист стажировки: стажировку начали раньше, чем проверку знания.</t>
+          <t>Нет номера записи в реестре. Протокол ЮГОК ПГУ 26-40, по программе 46б указано 77 часов.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>п. 25, п. 67</t>
+          <t>п. 92</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>К стажировке допускают работников, которые уже успешно прошли инструктаж по охране труда и обучение требованиям охраны труда по программам пункта 46. Обучение требованиям охраны труда заканчивается проверкой знания.</t>
+          <t>Регистрационный номер записи о прохождении проверки знания в реестре обученных лиц указывают в протоколе либо прикладывают подписанную электронной подписью выписку из реестра. 77 часов больше минимума в 16 часов и сами по себе не нарушение.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -584,23 +584,23 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Программы стажировки все без подписи.</t>
+          <t>К протоколу ЮГОК ПГУ 26-40 приложен лист стажировки: стажировку начали раньше, чем проверку знания.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>п. 28</t>
+          <t>п. 25, п. 67</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Программу стажировки на рабочем месте или иной локальный акт, которым задан ее объем, утверждает работодатель.</t>
+          <t>К стажировке допускают работников, которые уже успешно прошли инструктаж по охране труда и обучение требованиям охраны труда по программам пункта 46. Обучение требованиям охраны труда заканчивается проверкой знания.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -609,23 +609,23 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Программа 46а с 2023 года не утверждена.</t>
+          <t>Программы стажировки все без подписи.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>п. 48</t>
+          <t>п. 28</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Программу обучения требованиям охраны труда утверждает руководитель обучающей организации либо работодатель, если обучение проводит он.</t>
+          <t>Программу стажировки на рабочем месте или иной локальный акт, которым задан ее объем, утверждает работодатель.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -634,23 +634,23 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>В папке нет программы 46б.</t>
+          <t>Программа 46а с 2023 года не утверждена.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>п. 48, п. 96</t>
+          <t>п. 48</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Программа обучения требованиям охраны труда должна быть разработана и утверждена. Работодатель, который обучает своих работников, обязан иметь программы и учебные материалы для каждой программы.</t>
+          <t>Программу обучения требованиям охраны труда утверждает руководитель обучающей организации либо работодатель, если обучение проводит он.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -659,23 +659,23 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>В журнале первичного инструктажа на рабочем месте даты идут не в хронологическом порядке, есть склеенные листы.</t>
+          <t>В папке нет программы 46б.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>п. 87, п. 88</t>
+          <t>п. 48, п. 96</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>При регистрации инструктажа на рабочем месте указывают дату его проведения и остальные обязательные сведения. Порядок регистрации и форму утверждает работодатель. Запись должна позволять установить фактическую дату.</t>
+          <t>Программа обучения требованиям охраны труда должна быть разработана и утверждена. Работодатель, который обучает своих работников, обязан иметь программы и учебные материалы для каждой программы.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="72" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
@@ -684,23 +684,23 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Внеплановый инструктаж по изменениям не проводили с сентября.</t>
+          <t>В журнале первичного инструктажа на рабочем месте даты идут не в хронологическом порядке, есть склеенные листы.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>п. 16, п. 17</t>
+          <t>п. 87, п. 88</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Внеплановый инструктаж проводят, в частности, при изменении нормативных и локальных актов, которые затрагивают требования охраны труда и трудовые функции работника. Объем и сроки задает локальный акт работодателя.</t>
+          <t>При регистрации инструктажа на рабочем месте указывают дату его проведения и остальные обязательные сведения. Порядок регистрации и форму утверждает работодатель. Запись должна позволять установить фактическую дату.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="72" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
@@ -709,23 +709,23 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Проверку знания не проводят.</t>
+          <t>Внеплановый инструктаж по изменениям не проводили с сентября.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>п. 23, п. 67, п. 70</t>
+          <t>п. 16, п. 17</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Инструктаж по охране труда заканчивается проверкой знания требований охраны труда. Обучение по охране труда тоже завершается проверкой знания.</t>
+          <t>Внеплановый инструктаж проводят, в частности, при изменении нормативных и локальных актов, которые затрагивают требования охраны труда и трудовые функции работника. Объем и сроки задает локальный акт работодателя.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="72" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
@@ -734,48 +734,72 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>В офисе на участке протокол проверки знания без подписей.</t>
+          <t>Проверку знания не проводят.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>п. 93, п. 92</t>
+          <t>п. 23, п. 67, п. 70</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Протокол подписывают председатель и члены комиссии. В протоколе также должна быть подпись работника, прошедшего проверку знания.</t>
+          <t>Инструктаж по охране труда заканчивается проверкой знания требований охраны труда. Обучение по охране труда тоже завершается проверкой знания.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
       <c r="A12" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Несоответствие</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>В офисе на участке протокол проверки знания без подписей.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>п. 93, п. 92</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Протокол подписывают председатель и члены комиссии. В протоколе также должна быть подпись работника, прошедшего проверку знания.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Несоответствие</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Несоответствие</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Протокол ЮГОК ЭУ 26-26: программу 46б прошли по инструкции по охране труда.</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>п. 46, п. 48, п. 18</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Программа 46б — обучение безопасным методам при вредных и опасных факторах продолжительностью не менее 16 часов. Ее разрабатывают по примерному перечню тем и утверждают. Инструкция по охране труда задает объем инструктажа на рабочем месте и программу 46б не заменяет.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="72" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A2:E12"/>
+  <autoFilter ref="A2:E13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
